--- a/Result/profitability/2023.xlsx
+++ b/Result/profitability/2023.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.24</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.34625</v>
+        <v>-0.31125</v>
       </c>
       <c r="N2" t="n">
-        <v>7.93875</v>
+        <v>8.505000000000001</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.75</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.20375</v>
+        <v>-0.16875</v>
       </c>
       <c r="N3" t="n">
-        <v>8.776250000000001</v>
+        <v>9.231249999999999</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.47</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.09624999999999997</v>
+        <v>-0.09</v>
       </c>
       <c r="N4" t="n">
-        <v>9.372499999999999</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.72</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.16625</v>
+        <v>-0.09249999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>8.86125</v>
+        <v>9.295</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.27</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.1125</v>
+        <v>-0.05874999999999998</v>
       </c>
       <c r="N6" t="n">
-        <v>8</v>
+        <v>8.182500000000001</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.31</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.08374999999999996</v>
+        <v>-0.04374999999999998</v>
       </c>
       <c r="N7" t="n">
-        <v>7.056249999999999</v>
+        <v>7.42625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.34</v>
       </c>
       <c r="M8" t="n">
-        <v>0.01250000000000003</v>
+        <v>0.04875000000000002</v>
       </c>
       <c r="N8" t="n">
-        <v>7.37875</v>
+        <v>7.6125</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>0.115</v>
       </c>
       <c r="N9" t="n">
-        <v>7.6575</v>
+        <v>7.657499999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -1775,7 +1775,7 @@
         <v>0.03000000000000003</v>
       </c>
       <c r="N11" t="n">
-        <v>7.109999999999999</v>
+        <v>7.11</v>
       </c>
       <c r="O11" t="n">
         <v>1</v>
@@ -2029,7 +2029,7 @@
         <v>0.05000000000000003</v>
       </c>
       <c r="N13" t="n">
-        <v>6.2</v>
+        <v>6.199999999999999</v>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>17375</v>
+      </c>
+      <c r="D75" t="n">
+        <v>15566</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1809</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10.41</v>
+      </c>
+      <c r="G75" t="n">
+        <v>350</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2.01%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-582</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-233</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-195</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="N75" t="n">
+        <v>8.071249999999999</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7250000000000001</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>1.870000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2189695550351289</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.8428571428571429</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
